--- a/Result/profitability/2412.xlsx
+++ b/Result/profitability/2412.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM78"/>
+  <dimension ref="A1:AM79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,10 +667,10 @@
         <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2325</v>
+        <v>1.25875</v>
       </c>
       <c r="N2" t="n">
-        <v>38.1675</v>
+        <v>38.27375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -776,10 +776,10 @@
         <v>1.18</v>
       </c>
       <c r="M3" t="n">
-        <v>1.235</v>
+        <v>1.26125</v>
       </c>
       <c r="N3" t="n">
-        <v>39.2675</v>
+        <v>39.81375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -893,10 +893,10 @@
         <v>1.24</v>
       </c>
       <c r="M4" t="n">
-        <v>1.245</v>
+        <v>1.25875</v>
       </c>
       <c r="N4" t="n">
-        <v>40.98375</v>
+        <v>40.8375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1010,10 +1010,10 @@
         <v>0.99</v>
       </c>
       <c r="M5" t="n">
-        <v>1.21125</v>
+        <v>1.21875</v>
       </c>
       <c r="N5" t="n">
-        <v>41.4125</v>
+        <v>41.3075</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>1.12</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1875</v>
+        <v>1.20625</v>
       </c>
       <c r="N6" t="n">
-        <v>42.2025</v>
+        <v>42.2525</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1256,10 +1256,10 @@
         <v>1.31</v>
       </c>
       <c r="M7" t="n">
-        <v>1.19875</v>
+        <v>1.22</v>
       </c>
       <c r="N7" t="n">
-        <v>43.295</v>
+        <v>43.78375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1268,7 +1268,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1383,10 +1383,10 @@
         <v>1.39</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2225</v>
+        <v>1.23125</v>
       </c>
       <c r="N8" t="n">
-        <v>44.45500000000001</v>
+        <v>44.4075</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1640,7 +1640,7 @@
         <v>1.1525</v>
       </c>
       <c r="N10" t="n">
-        <v>43.99874999999999</v>
+        <v>43.99875</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -2021,7 +2021,7 @@
         <v>1.13875</v>
       </c>
       <c r="N13" t="n">
-        <v>43.445</v>
+        <v>43.44499999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -10326,6 +10326,133 @@
       </c>
       <c r="AM78" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>61363</v>
+      </c>
+      <c r="D79" t="n">
+        <v>38328</v>
+      </c>
+      <c r="E79" t="n">
+        <v>23035</v>
+      </c>
+      <c r="F79" t="n">
+        <v>37.54</v>
+      </c>
+      <c r="G79" t="n">
+        <v>13261</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>21.61%</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>691</v>
+      </c>
+      <c r="J79" t="n">
+        <v>13953</v>
+      </c>
+      <c r="K79" t="n">
+        <v>10641</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.2475</v>
+      </c>
+      <c r="N79" t="n">
+        <v>36.6475</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
+      </c>
+      <c r="V79" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0.05384615384615388</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>-0.3800000000000026</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>-0.01002109704641352</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0.06000000000000005</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0.04580152671755733</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>-0.8400000000000034</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>-0.02188639916623247</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK79" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
